--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="265">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,200 +347,330 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.documentId</t>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader</t>
+  </si>
+  <si>
+    <t>Innehåller basinformation om dokumentet</t>
+  </si>
+  <si>
+    <t>Innehåller basinformation om dokumentet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.documentId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivString
+</t>
   </si>
   <si>
     <t>Planens identitet, unik inom källsystemet</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.sourceSystemHSAId</t>
+    <t>Vård- och omsorgsplanens identitet som är unik inom källsystemet. Identifieraren ska vara konsistent och beständigt mellan olika majorversioner av ett kontrakt. Ett exempel på detta är att en vårdkontakt ska ha samma identifierare i majorversion 3 och 4 av ett tjänstekontrakt för att läsa vårdkontakter. Identifieraren ska vara konsistent och beständigt mellan olika kontrakt. Ett exempel på detta är att samma remiss-identitet ska användas i ett tjänstekontrakt för att läsa remisser, samt tjänstekontraktet som läser remissvar som refererar till den ursprungliga remissen.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.sourceSystemHSAId</t>
   </si>
   <si>
     <t>HSA-id för källsystemet</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.documentTitle</t>
+    <t>HSA-id för det system som dokumentet är skapat i.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.documentTitle</t>
   </si>
   <si>
     <t>Rubrik för vård- och omsorgsplanen</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.documentTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>Text som innehåller en rubrik som beskriver innehållet i vård- och omsorgsplanen. För att underlätta för användaren att orientera sig i gränssnittet är det viktigt att ange en deskriptiv text i attributet rubrik. Inga krav finns dock på struktur för detta. Exempel: Samordnad vårdplanering Rehabiliteringsplan.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.documentTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivTimeStamp
 </t>
   </si>
   <si>
     <t>Tidpunkt då planen upprättades (YYYYMMDDhhmmss)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.patientId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
+    <t>Tidpunkt då vård- och omsorgsplanen upprättats.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.patientId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivPersonIdTypeLogisticsLogistics3
 </t>
   </si>
   <si>
     <t>Patientens identifierare (personnummer/samordningsnummer)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional</t>
+    <t>Id för patienten.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional</t>
   </si>
   <si>
     <t>Ansvarig hälso- och sjukvårdspersonal</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.authorTime</t>
+    <t>Hälso- och sjukvårdspersonal som ansvarar för vård- och omsorgsplanen.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.authorTime</t>
   </si>
   <si>
     <t>Tidpunkt då informationen registrerades (YYYYMMDDhhmmss)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalHSAId</t>
+    <t>Tidpunkt då informationen registrerades. Regel: Regel 2
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalHSAId</t>
   </si>
   <si>
     <t>HSA-id för ansvarig personal</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalName</t>
+    <t>HSA-id för hälso- och sjukvårdspersonal som ansvar för vårdplanen.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalName</t>
   </si>
   <si>
     <t>Namn på ansvarig personal</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalRoleCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
+    <t>Namn på hälso- och sjukvårdspersonal.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalRoleCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivCVTypeLogisticsLogistics3
 </t>
   </si>
   <si>
     <t>Befattning (KV Befattning OID 1.2.752.129.2.2.1.4)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit</t>
+    <t>Information om hälso- och sjukvårdspersonalens befattning. Om möjligt ska KV Befattning (OID 1.2.752.129.2.2.1.4) användas. Se referens [R6].</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit</t>
   </si>
   <si>
     <t>Organisationsenhet för ansvarig personal</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitHSAId</t>
+    <t>Den organisation som hälso- och sjukvårdspersonalen är uppdragstagare på. Regel: Regel 4</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitHSAId</t>
   </si>
   <si>
     <t>HSA-id för org.enhet</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitName</t>
+    <t>HSA-id för organisationsenhet. Regel: Regel 4</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitName</t>
   </si>
   <si>
     <t>Namn på org.enhet</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitTelecom</t>
+    <t>Namnet på den organisation som den ansvariga hälso- och sjukvårdspersonalen är uppdragstagare på. Regel: Regel 4</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitTelecom</t>
   </si>
   <si>
     <t>Telefon till org.enhet</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitEmail</t>
+    <t>Telefon till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitEmail</t>
   </si>
   <si>
     <t>E-post till org.enhet</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitAddress</t>
+    <t>Epost till enhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitAddress</t>
   </si>
   <si>
     <t>Postadress för org.enhet</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitLocation</t>
+    <t>Postadress för den organisation som hälso- och sjukvårdspersonal en är uppdragstagare på. Skrivs på ett så naturligt sätt som möjligt, exempelvis: ”Storgatan 12 468 91 Lilleby”</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitLocation</t>
   </si>
   <si>
     <t>Plats för org.enhet</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalCareUnitHSAId</t>
+    <t>Text som anger namnet på plats eller ort för organisationens fysiska placering.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalCareUnitHSAId</t>
   </si>
   <si>
     <t>HSA-id för vårdenhet (Regel 1: PDL/Sparr)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.accountableHealthcareProfessional.healthcareProfessionalCareGiverHSAId</t>
+    <t>HSA-id för vårdenhet. Regel: Regel 1</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.accountableHealthcareProfessional.healthcareProfessionalCareGiverHSAId</t>
   </si>
   <si>
     <t>HSA-id för vårdgivare (Regel 1: PDL/Sparr)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.legalAuthenticator</t>
+    <t>HSA-id för vårdgivaren, som är vårdgivare för den enhet som hälso- och sjukvårdspersonalalen är uppdragstagare för. Regel: Regel 1</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.legalAuthenticator</t>
   </si>
   <si>
     <t>Signeringsinformation</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.legalAuthenticator.id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.legalAuthenticator.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.legalAuthenticator.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.legalAuthenticator.signatureTime</t>
+    <t>Information om vem som signerat informationen i dokumentet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.legalAuthenticator.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.legalAuthenticator.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.legalAuthenticator.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.legalAuthenticator.signatureTime</t>
   </si>
   <si>
     <t>Tidpunkt för signering (YYYYMMDDhhmmss)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.legalAuthenticator.legalAuthenticatorHSAId</t>
+    <t>Tidpunkt för signering
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.legalAuthenticator.legalAuthenticatorHSAId</t>
   </si>
   <si>
     <t>HSA-id för signerare</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.legalAuthenticator.legalAuthenticatorName</t>
+    <t>HSA-id för person som signerat dokumentet</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.legalAuthenticator.legalAuthenticatorName</t>
   </si>
   <si>
     <t>Namn på signerare</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.approvedForPatient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
+    <t>Namnen i klartext för signerande person.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.approvedForPatient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivBoolean
 </t>
   </si>
   <si>
     <t>Informationen godkänd för patient (Regel 3)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.careContactId</t>
+    <t>Anger om information får delas till patient. Värdet sätts i sådant fall till true, i annat fall till false. Regel: Regel 3</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.nullified</t>
+  </si>
+  <si>
+    <t>Makulerad</t>
+  </si>
+  <si>
+    <t>Ska ej anges</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.nullifiedReason</t>
+  </si>
+  <si>
+    <t>Makuleringsorsak</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanHeader.careContactId</t>
   </si>
   <si>
     <t>Refererad vårdkontakt-id</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.content</t>
+    <t>Identitetet för den vårdkontakt som föranlett den information som omfattas av dokumentet. Identiteten är unik inom källsystemet</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody</t>
+  </si>
+  <si>
+    <t>carePlanBody</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.content</t>
   </si>
   <si>
     <t>Innehåll i vård- och omsorgsplanen (MultimediaType)</t>
@@ -553,7 +683,16 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.content.id</t>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.content.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.content.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.content.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.content.rivId</t>
   </si>
   <si>
     <t>id (ej tillämpligt)</t>
@@ -562,66 +701,88 @@
     <t>N/A — content.id är 0..0 per TKB för GetCarePlans.</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.content.extension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.content.modifierExtension</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.content.mediaType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.content.mediaType</t>
+  </si>
+  <si>
+    <t>Mediatyp (MIME-typ): text/plain, text/html, image/jpeg, image/png, image/tiff, application/pdf</t>
+  </si>
+  <si>
+    <t>Typ av multimedia (enligt HL7). Följande format för mediatype kan tillämpas i denna version: text/plain text/html image/png image/jpeg image/tiff application/pdf
+Tillåtna värden enligt XSD: application/dicom, application/msword, application/pdf, audio/basic, audio/k32adpcm, audio/mpeg, image/g3fax, image/gif, image/jpeg, image/png, image/tiff, model/vrml, multipart/x-hl7-cda-level1, text/html, text/plain, text/rtf, text/sgml, text/x-hl7-ft, text/xml, video/mpeg, video/x-avi.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.content.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivBase64Binary
 </t>
   </si>
   <si>
-    <t>Mediatyp (MIME-typ): text/plain, text/html, image/jpeg, image/png, image/tiff, application/pdf</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.content.value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">base64Binary
+    <t>Binärdata (base64) – XOR med reference</t>
+  </si>
+  <si>
+    <t>Value är binärdata som representerar objektet. Ett och endast ett av attributen value och reference ska anges.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.content.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivAnyURI
 </t>
   </si>
   <si>
-    <t>Binärdata (base64) – XOR med reference</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.content.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url
+    <t>Referens till extern fil (URL) – XOR med value</t>
+  </si>
+  <si>
+    <t>Referens till extern binär fil i form av en URL. Ett och endast ett av attributen value och reference ska anges.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.participatingCareUnitHSAId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivIITypeLogisticsLogistics3
 </t>
   </si>
   <si>
-    <t>Referens till extern fil (URL) – XOR med value</t>
-  </si>
-  <si>
-    <t>SEEHDSLMCarePlans.carePlan.participatingCareUnitHSAId</t>
-  </si>
-  <si>
     <t>Deltagande vårdenheters HSA-id (IIType)</t>
   </si>
   <si>
-    <t>SEEHDSLMCarePlans.carePlan.typeOfCarePlan</t>
+    <t>En Vård- och omsorgsplan har noll eller flera deltagande enheter.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.typeOfCarePlanEnum</t>
   </si>
   <si>
     <t>Typ av vård- och omsorgsplan</t>
   </si>
   <si>
+    <t>Tillåtna värden enligt XSD: SIP, SPLPTLRV, SPU, VP, HP, RP, GP, SVP.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCarePlans.carePlan.carePlanBody.typeOfCarePlanEnum.value</t>
+  </si>
+  <si>
+    <t>Elementets textinnehåll</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
     <t>https://fhir.inera.se/ig/ehds-tk/ValueSet/typeofcareplan-vs</t>
   </si>
   <si>
+    <t>SEEHDSRivString.value</t>
+  </si>
+  <si>
     <t>SEEHDSLMCarePlans.result</t>
   </si>
   <si>
     <t>Resultatkod för anropet</t>
   </si>
   <si>
+    <t>Innehåller information om begäran gick bra eller ej.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCarePlans.result.id</t>
   </si>
   <si>
@@ -637,28 +798,45 @@
     <t>Resultatkod: OK, INFO eller ERROR</t>
   </si>
   <si>
+    <t>Kan endast vara OK, INFO eller ERROR
+Tillåtna värden enligt XSD: OK, ERROR, INFO.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCarePlans.result.errorCode</t>
   </si>
   <si>
     <t>Felkod vid ERROR (INVALID_REQUEST)</t>
   </si>
   <si>
+    <t>Sätts endast om resultCode är ERROR, se kapitel 4.4 för mer information.
+Tillåtna värden enligt XSD: INVALID_REQUEST.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCarePlans.result.logId</t>
   </si>
   <si>
     <t>UUID för felsökning</t>
   </si>
   <si>
+    <t>En UUID som kan användas vid felanmälan för att användas vid felsökning av producent.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCarePlans.result.subCode</t>
   </si>
   <si>
     <t>Subkod</t>
   </si>
   <si>
+    <t>Inga subkoder är specificerade.</t>
+  </si>
+  <si>
     <t>SEEHDSLMCarePlans.result.message</t>
   </si>
   <si>
     <t>Beskrivande meddelande (svenska)</t>
+  </si>
+  <si>
+    <t>En beskrivande text som kan visas för användaren.</t>
   </si>
 </sst>
 </file>
@@ -960,11 +1138,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="92.10546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="92.10546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="105.11328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="105.11328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -973,7 +1151,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.48046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -994,7 +1172,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="90.3515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="103.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1644,13 +1822,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>107</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1713,15 +1891,15 @@
         <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1729,7 +1907,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>83</v>
@@ -1747,10 +1925,10 @@
         <v>84</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1801,10 +1979,10 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>83</v>
@@ -1825,14 +2003,14 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>72</v>
@@ -1844,15 +2022,17 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>72</v>
@@ -1889,71 +2069,75 @@
         <v>72</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>72</v>
       </c>
@@ -2001,27 +2185,27 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2044,13 +2228,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2101,7 +2285,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
@@ -2118,10 +2302,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2144,13 +2328,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2201,7 +2385,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -2213,15 +2397,15 @@
         <v>72</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2229,7 +2413,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>83</v>
@@ -2244,13 +2428,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2301,10 +2485,10 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>83</v>
@@ -2318,21 +2502,21 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
@@ -2344,17 +2528,15 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>72</v>
@@ -2391,75 +2573,71 @@
         <v>72</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>72</v>
       </c>
@@ -2507,27 +2685,27 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2550,13 +2728,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2607,7 +2785,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -2619,15 +2797,15 @@
         <v>72</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2653,10 +2831,10 @@
         <v>84</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2707,7 +2885,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2724,21 +2902,21 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>72</v>
@@ -2750,15 +2928,17 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>72</v>
@@ -2795,71 +2975,75 @@
         <v>72</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>72</v>
       </c>
@@ -2907,27 +3091,27 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2935,7 +3119,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>83</v>
@@ -2950,13 +3134,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3007,10 +3191,10 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>83</v>
@@ -3019,15 +3203,15 @@
         <v>72</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3050,13 +3234,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3107,7 +3291,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -3124,21 +3308,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>72</v>
@@ -3150,17 +3334,15 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>72</v>
@@ -3197,75 +3379,71 @@
         <v>72</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>72</v>
       </c>
@@ -3313,27 +3491,27 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3356,13 +3534,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3413,7 +3591,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3425,15 +3603,15 @@
         <v>72</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3459,10 +3637,10 @@
         <v>84</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3513,7 +3691,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3530,21 +3708,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>72</v>
@@ -3556,15 +3734,17 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>72</v>
@@ -3601,71 +3781,75 @@
         <v>72</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>72</v>
       </c>
@@ -3713,27 +3897,27 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3756,13 +3940,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3813,7 +3997,7 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>73</v>
@@ -3830,10 +4014,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3856,13 +4040,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3913,7 +4097,7 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
@@ -3930,10 +4114,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3956,13 +4140,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4013,7 +4197,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
@@ -4030,10 +4214,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4056,13 +4240,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4113,7 +4297,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4130,10 +4314,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4156,13 +4340,13 @@
         <v>72</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4213,7 +4397,7 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -4225,15 +4409,15 @@
         <v>72</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4256,13 +4440,13 @@
         <v>72</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4313,7 +4497,7 @@
         <v>72</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
@@ -4330,21 +4514,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>72</v>
@@ -4356,17 +4540,15 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>72</v>
@@ -4403,75 +4585,71 @@
         <v>72</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>72</v>
       </c>
@@ -4519,27 +4697,27 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4547,7 +4725,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>83</v>
@@ -4562,13 +4740,13 @@
         <v>72</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4619,10 +4797,10 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>83</v>
@@ -4631,15 +4809,15 @@
         <v>72</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4665,10 +4843,10 @@
         <v>84</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4719,7 +4897,7 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
@@ -4736,21 +4914,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>72</v>
@@ -4762,15 +4940,17 @@
         <v>72</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>72</v>
@@ -4807,71 +4987,75 @@
         <v>72</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>72</v>
       </c>
@@ -4919,27 +5103,27 @@
         <v>72</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4947,7 +5131,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>83</v>
@@ -4962,13 +5146,13 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5019,10 +5203,10 @@
         <v>72</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>83</v>
@@ -5036,10 +5220,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5050,7 +5234,7 @@
         <v>73</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>72</v>
@@ -5062,13 +5246,13 @@
         <v>72</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5119,27 +5303,27 @@
         <v>72</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>172</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5150,7 +5334,7 @@
         <v>73</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>72</v>
@@ -5162,13 +5346,13 @@
         <v>72</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5219,7 +5403,7 @@
         <v>72</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -5236,21 +5420,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>72</v>
@@ -5262,17 +5446,15 @@
         <v>72</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>72</v>
@@ -5309,75 +5491,71 @@
         <v>72</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>72</v>
       </c>
@@ -5425,27 +5603,27 @@
         <v>72</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5453,10 +5631,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
@@ -5468,13 +5646,13 @@
         <v>72</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5525,13 +5703,13 @@
         <v>72</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>72</v>
@@ -5542,10 +5720,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5568,13 +5746,13 @@
         <v>72</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5625,7 +5803,7 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
@@ -5642,10 +5820,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5653,7 +5831,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>83</v>
@@ -5668,13 +5846,13 @@
         <v>72</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5725,10 +5903,10 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>83</v>
@@ -5737,15 +5915,15 @@
         <v>72</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5756,7 +5934,7 @@
         <v>73</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>72</v>
@@ -5768,13 +5946,13 @@
         <v>72</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>188</v>
+        <v>86</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5825,13 +6003,13 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>72</v>
@@ -5842,21 +6020,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>72</v>
@@ -5868,15 +6046,17 @@
         <v>72</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>190</v>
+        <v>91</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>72</v>
@@ -5901,81 +6081,87 @@
         <v>72</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>72</v>
       </c>
@@ -6023,27 +6209,27 @@
         <v>72</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6054,7 +6240,7 @@
         <v>73</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>72</v>
@@ -6066,13 +6252,13 @@
         <v>72</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>85</v>
+        <v>212</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6123,38 +6309,38 @@
         <v>72</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>72</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>72</v>
@@ -6166,17 +6352,15 @@
         <v>72</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>72</v>
@@ -6213,43 +6397,43 @@
         <v>72</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -6262,26 +6446,24 @@
         <v>72</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O53" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>72</v>
       </c>
@@ -6317,19 +6499,19 @@
         <v>72</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
@@ -6346,42 +6528,46 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>72</v>
       </c>
@@ -6429,27 +6615,27 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6460,7 +6646,7 @@
         <v>73</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>72</v>
@@ -6472,13 +6658,13 @@
         <v>72</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6529,13 +6715,13 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>72</v>
@@ -6546,10 +6732,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6572,13 +6758,13 @@
         <v>72</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6629,7 +6815,7 @@
         <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -6646,10 +6832,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6672,13 +6858,13 @@
         <v>72</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -6729,7 +6915,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
@@ -6746,10 +6932,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6772,13 +6958,13 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -6829,7 +7015,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>73</v>
@@ -6841,6 +7027,1210 @@
         <v>72</v>
       </c>
       <c r="AJ58" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="Y61" s="2"/>
+      <c r="Z61" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCarePlans.xlsx
+++ b/StructureDefinition-SEEHDSLMCarePlans.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
